--- a/public/Calculadora-de-Ahorro-Estrategico-GTC.xlsx
+++ b/public/Calculadora-de-Ahorro-Estrategico-GTC.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="🧮 Calculadora" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E15" s="51"/>
       <c r="F15" s="56">
-        <f>IF(C11="Junior",1200*12,IF(C11="Mid",1400*12,IF(C11="Senior",1650*12,0)))</f>
+        <f>IF(C11="Junior",1300*12,IF(C11="Mid",1400*12,IF(C11="Senior",1650*12,0)))</f>
         <v>19800</v>
       </c>
       <c r="G15" s="57">
